--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
@@ -266,7 +266,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 rat-1:分子と分母の両方が存在するか、両方が存在します。両方が欠席している場合、いくつかの拡張が存在するものとします / Numerator and denominator SHALL both be present, or both are absent. If both are absent, there SHALL be some extension present {(numerator.empty() xor denominator.exists()) and (numerator.exists() or extension.exists())}</t>
   </si>
   <si>
@@ -331,7 +331,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -348,7 +348,7 @@
     <t>薬剤に関する数量と単位を定めている。ValueおよびCodeを必須としている。単位についてはMERIT9医薬品単位略号の利用を推進している。(**SHOULD**)</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
   </si>
   <si>
@@ -383,7 +383,7 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -580,7 +580,7 @@
     <t>一部のユニット表現システムのユニットのコンピューター処理可能な形式。 / A computer processable form of the unit in some unit representation system.</t>
   </si>
   <si>
-    <t>優先システムはUCUMですが、スノムCTは（慣習ユニットに）または通貨にISO 4217を使用することもできます。使用のコンテキストには、特定のシステムからのコードがさらに必要になる場合があります。 / The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+    <t>優先システムはUCUMですが、独自の単位にはSNOMED-CT、または通貨にISO 4217を使用することもできます。使用のコンテキストには、特定のシステムからのコードがさらに必要になる場合があります。 / The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/units-of-time</t>
